--- a/sheets/대금율보/검수/남도 방아 타령.xlsx
+++ b/sheets/대금율보/검수/남도 방아 타령.xlsx
@@ -2468,8 +2468,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ʒ
-‹</t>
+          <t xml:space="preserve">淋ʒ</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -2479,8 +2478,7 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -2492,8 +2490,7 @@
         <is>
           <t xml:space="preserve">潢
 汰
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
@@ -2613,8 +2610,7 @@
         <is>
           <t xml:space="preserve">浹
 汰
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -2626,8 +2622,7 @@
         <is>
           <t xml:space="preserve">浹
 浹
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -2639,8 +2634,7 @@
         <is>
           <t xml:space="preserve">潢
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
@@ -2764,8 +2758,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -2777,8 +2770,7 @@
         <is>
           <t xml:space="preserve">潢
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -2790,8 +2782,7 @@
         <is>
           <t xml:space="preserve">林
 南
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
@@ -2885,8 +2876,7 @@
         <is>
           <t xml:space="preserve">浹
 浹
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -2898,8 +2888,7 @@
         <is>
           <t xml:space="preserve">浹
 汰
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">

--- a/sheets/대금율보/검수/남도 방아 타령.xlsx
+++ b/sheets/대금율보/검수/남도 방아 타령.xlsx
@@ -2331,18 +2331,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="86.96" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="97.23" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="97.23" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="97.23" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="97.23" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="97.23" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="97.23" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="97.23" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="97.23" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="97.23" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="97.23" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="97.23" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="97.23" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="97.23" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="97.23" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -2839,7 +2839,7 @@
       <c r="F16" s="21"/>
       <c r="G16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="97.23" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="97.23" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -2903,6 +2903,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
 </worksheet>
 </file>